--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0062.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0062.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Chi Tiết Giai Đoạn Luyện Hợp Kim II</t>
+          <t>Chi Tiết Giai Đoạn Nấu Luyện Hợp Kim II</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Chi Tiết Giai Đoạn Luyện Hợp Kim II</t>
+          <t>Chi Tiết Giai Đoạn Nấu Luyện Hợp Kim II</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Chi Tiết Giai Đoạn Luyện Hợp Kim II</t>
+          <t>Chi Tiết Giai Đoạn Nấu Luyện Hợp Kim II</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Chi Tiết Giai Đoạn Luyện Hợp Kim II</t>
+          <t>Chi Tiết Giai Đoạn Nấu Luyện Hợp Kim II</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>By Moon's Grace</t>
+          <t>Nhờ Ân Huệ của Mặt Trăng</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Popularity</t>
+          <t>Độ nổi tiếng</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Gian hàng Hội Chợ</t>
+          <t>Gian Hàng Hội Chợ</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Điều Ước Lều Trại</t>
+          <t>Điều Ước Nhà Trọ</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Lodge Wishes Rules</t>
+          <t>Quy Tắc Điều Ước Nhà Trọ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Companions</t>
+          <t>Đồng Hành</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Tương Tác Với Đồng Hành</t>
+          <t>Tương tác với Đồng Hành</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Sailing Time</t>
+          <t>Thời Gian Hành Trình</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Durability</t>
+          <t>Độ bền</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Fame</t>
+          <t>Danh vọng</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Locked Requests</t>
+          <t>Yêu cầu đã khóa</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Tường Đổ &amp; Mảnh Vỡ</t>
+          <t>Tường Sụp &amp; Mảnh Vỡ</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Tường Đổ &amp; Mảnh Vỡ</t>
+          <t>Tường Sụp &amp; Mảnh Vỡ</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Magnetic Cube: II</t>
+          <t>Khối Từ Tính: II</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Magnetic Cube: III</t>
+          <t>Khối Từ Tính: III</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Tacet Field: Special Bonus</t>
+          <t>Tổ Tacet: Phần Thưởng Đặc Biệt</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Phantom Discord</t>
+          <t>Tacet Discord Ảo Giác</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Tacet Field: Special Bonus</t>
+          <t>Tổ Tacet: Phần Thưởng Đặc Biệt</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Phantom Discord</t>
+          <t>Tacet Discord Ảo Giác</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Kỹ Năng Phản Đòn</t>
+          <t>Kỹ năng phản đòn</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Điểm Lưu Đã Được Cập Nhật</t>
+          <t>Đã cập nhật điểm lưu</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Echo Hunters</t>
+          <t>Thợ Săn Tiếng Vọng</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Chạm Để Xem Hướng Dẫn</t>
+          <t>Chạm để xem Hướng Dẫn</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Kẻ Địch Đặc Biệt</t>
+          <t>Kẻ Thù Đặc Biệt</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Lumiscale Construct</t>
+          <t>Cấu Trúc Vảy Quang</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Lumiscale Construct</t>
+          <t>Cấu Trúc Vảy Quang</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Chronosorter</t>
+          <t>Bộ Phân Loại Thời Gian</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Photonvault &amp; Photon Barrier</t>
+          <t>Hầm Photon &amp; Rào Chắn Photon</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Flare Crest &amp; Flare Stone</t>
+          <t>Huy Hiệu Lửa &amp; Đá Lửa</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Thử Thách Echo: Clang Bang I</t>
+          <t>Thử Thách Tiếng Vọng: Clang Bang I</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Thử Thách Echo: Clang Bang II</t>
+          <t>Thử Thách Tiếng Vọng: Clang Bang II</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Thiết bị Leap</t>
+          <t>Thiết Bị Nhảy Cao</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Windchimer</t>
+          <t>Thú Gió</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Ice Pile</t>
+          <t>Đống Băng</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Light Emitter &amp; Light Gatherer</t>
+          <t>Bộ Thu và Phát Quang</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Stone Lift</t>
+          <t>Nâng Đá</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Ski</t>
+          <t>Hologram Chiến Thuật: Ski</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Frostbug</t>
+          <t>Bọ Sương</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Nghi Lễ Dâng Hiến: Ngọc Trai</t>
+          <t>Nghi Thức Dâng Tế: Ngọc Trai</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Offering Site Entrance</t>
+          <t>Lối Vào Địa Điểm Dâng Hiến</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Sagaci Springs</t>
+          <t>Suối Sagaci</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>About Tactical Simulacra</t>
+          <t>Về Chiến Dịch Mô Phỏng Chiến Thuật</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>About Memetic Tuning</t>
+          <t>Về Điều Chỉnh Ngữ Nghĩa</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Tỷ lệ rơi vật phẩm tăng cường</t>
+          <t>Tỷ Lệ Rơi Vật Phẩm Cường Hóa</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>About Lollo Campaign</t>
+          <t>Về Chiến Dịch Lollo</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Về Những Câu Chuyện từ Núi Firmament</t>
+          <t>Về Những Câu Chuyện từ Núi Thiên Cung</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Quy Tắc Sự Kiện Quà Tặng Ánh Sáng Thiên Giới</t>
+          <t>Thể lệ sự kiện Quà tặng Ánh Sáng Thiên Giới</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Về Sự Trở Lại của Thủy Triều</t>
+          <t>Về *Reprise of Tides*</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Chronosorter I</t>
+          <t>Bộ Phân Loại Thời Gian I</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Chronosorter II</t>
+          <t>Bộ Phân Loại Thời Gian II</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Photonvault &amp; Rào Chắn Photon</t>
+          <t>Hầm Photon &amp; Rào Chắn Photon</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Huy Hiệu Flare &amp; Đá Flare</t>
+          <t>Huy Hiệu Lửa &amp; Đá Lửa</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Missing Ice Cube</t>
+          <t>Thiếu Ice Cube</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Breaking Ice Walls</t>
+          <t>Phá Băng Giá</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Breaking Ice Caps</t>
+          <t>Phá Vỡ Các Mỏm Băng</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Thiết bị Leap</t>
+          <t>Thiết Bị Nhảy Cao</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Windchimer</t>
+          <t>Thú Gió</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Ice Pile</t>
+          <t>Đống Băng</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Light Emitter</t>
+          <t>Bộ Phát Quang</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Light Gatherer</t>
+          <t>Bộ Thu Quang</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Stone Lift</t>
+          <t>Nâng Đá</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Ski</t>
+          <t>Trượt tuyết</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Acceleration Ring</t>
+          <t>Nhẫn Tăng Tốc</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Point Ring</t>
+          <t>Vòng Điểm</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Bonus Ring</t>
+          <t>Vòng Phần Thưởng</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Frostbug</t>
+          <t>Bọ Sương</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Nghi Lễ Dâng Hiến: Ngọc Trai</t>
+          <t>Nghi Thức Dâng Tế: Ngọc Trai</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Offering Site Entrance</t>
+          <t>Lối Vào Địa Điểm Dâng Hiến</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Sagaci Springs</t>
+          <t>Suối Sagaci</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Xác định mẫu và tìm vị trí cùng hướng phù hợp nhất cho Clang Bang</t>
+          <t>Phân tích mô hình và tìm vị trí, tư thế phù hợp nhất để đặt Clang Bang</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Vị Trí và Hướng Đối Diện</t>
+          <t>Vị Trí và Hướng Đứng</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Aerial Sickle Attack 1</t>
+          <t>Đòn Liềm Trên Không 1</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Aerial Sickle Attack 2</t>
+          <t>Đòn Liềm Trên Không 2</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Aerial Sickle Attack 3</t>
+          <t>Đòn Liềm Trên Không 3</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Aerial Scythe Attack 2</t>
+          <t>Đòn Hái Trên Không 2</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Aerial Scythe Attack 3</t>
+          <t>Đòn Hái Trên Không 3</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Plunging Attack</t>
+          <t>Tấn Công Đâm Xuống</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Special BA</t>
+          <t>BA Đặc Biệt</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Special Mid-air Attack</t>
+          <t>Đòn Tấn Công Giữa Không Trung Đặc Biệt</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Enhanced BA</t>
+          <t>BA Nâng Cao</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Enhanced HA</t>
+          <t>Tấn Công Nặng Cường Hóa</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Plunging Attack</t>
+          <t>Tấn Công Đâm Xuống</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Sự Kiện Mới "Liệu Echoid Có Mơ Về Cừu Điện Không?" Đã Có Thể Tham Gia!</t>
+          <t>Sự Kiện Mới "Liệu Sinh Vật Echo Có Mơ Về Cừu Điện Không?" Đã Có!</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Về Quà Tặng Ánh Trăng Rực Rỡ</t>
+          <t>Về Quà Tặng Ánh Trăng Rằm</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Converging Paths</t>
+          <t>Những con đường hội tụ</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Sử Dụng Intro Skill và Outro Skill Trong Chế Độ Đồng Đội</t>
+          <t>Kích hoạt Kỹ Năng Giới Thiệu và Kỹ Năng Kết trong Chế Độ Đồng Đội</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Sử Dụng Intro Skill và Outro Skill Trong Chế Độ Đồng Đội</t>
+          <t>Kích hoạt Kỹ Năng Giới Thiệu và Kỹ Năng Kết trong Chế Độ Đồng Đội</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Chrono Sign</t>
+          <t>Dấu Hiệu Thời Gian</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Kích Hoạt Prototype Chronosorter</t>
+          <t>Kích hoạt Prototype Chronosorter</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Malfunctioning Stone Lift</t>
+          <t>Thang máy đá bị lỗi</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Chrono Sign</t>
+          <t>Dấu Hiệu Thời Gian</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Kích Hoạt Prototype Chronosorter</t>
+          <t>Kích hoạt Prototype Chronosorter</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Malfunctioning Stone Lift</t>
+          <t>Thang máy đá bị lỗi</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Màu Đỏ Rực Cháy Trong Ký Ức</t>
+          <t>Lửa Đỏ Trong Ký Ức</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Lollo Express: Promise Delivered</t>
+          <t>Lollo Express: Lời Hứa Đã Thực Hiện</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Nảy Bóng Sao</t>
+          <t>Vụ nổ sao</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Chuyến Tham quan Tìm Kiếm Dải Ngân Hà</t>
+          <t>Chuyến Du Ngoạn Kiếm Thức Thiên Hà</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Đường Đua Vô Tận Dải Ngân Hà</t>
+          <t>Đường Đua Dải Ngân Hà Vô Tận</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Dự báo thời tiết Solaris</t>
+          <t>Dự báo Thời tiết Solaris</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Trung Tâm Dữ Liệu</t>
+          <t>Trung tâm dữ liệu</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Mô phỏng Chiến đấu Vô tận</t>
+          <t>Mô Phỏng Chiến Đấu Vô Tận</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Nơi Những Vì Sao An Giấc</t>
+          <t>Nơi Sao An Giấc</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>About Mail Hệ thống</t>
+          <t>Về Hệ Thống Thư</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Lollo Campaign: Rerun</t>
+          <t>Chiến Dịch Lollo: Tái Diễn</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Plunge Mechanism</t>
+          <t>Cơ Chế Lao Xuống</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Bounce Pad</t>
+          <t>Bệ Bật</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Outlier: Discord</t>
+          <t>Dị Thể: Tacet Discord</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Tethys Terminal: Cleansing Corruption</t>
+          <t>Thiết bị đầu cuối Tethys: Thanh Tẩy Tham Nhiễm</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Tethys Terminal: Opening One Portal</t>
+          <t>Thiết bị đầu cuối Tethys: Mở Một Cổng Kết Nối</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Tethys Terminal: Opening Two Portals</t>
+          <t>Thiết bị đầu cuối Tethys: Mở Hai Cổng Kết Nối</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Data Overflow</t>
+          <t>Dữ liệu Tràn Bộ Nhớ</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Activating Key</t>
+          <t>Đang kích hoạt chìa khóa</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Barriers</t>
+          <t>Rào Cản</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Sử Dụng Cổng Để Xóa Corruption</t>
+          <t>Dùng Cổng để Xóa Nhiễm Độc</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Plunge Mechanism</t>
+          <t>Cơ Chế Lao Xuống</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Bounce Pad</t>
+          <t>Bệ Bật</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Outlier: Discord</t>
+          <t>Dị Thể: Tacet Discord</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Tethys Terminal: Cleansing Corruption</t>
+          <t>Thiết bị đầu cuối Tethys: Thanh Tẩy Tham Nhiễm</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Opening Portals</t>
+          <t>Mở Cánh Cổng Không Gian</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Đi Qua Các Cổng</t>
+          <t>Đi Xuyên Cổng Không Gian</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Mặt Sau của Bức Tường Dữ Liệu</t>
+          <t>Mặt Sau Bức Tường Dữ Liệu</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Tethys Terminal: Opening Two Portals</t>
+          <t>Thiết bị đầu cuối Tethys: Mở Hai Cổng Kết Nối</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Thu thập Aetherfin để duy trì năng lượng</t>
+          <t>Thu thập Cá Tinh Khiết để duy trì Năng lượng</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Avoiding Red Rings</t>
+          <t>Tránh Vòng Đỏ</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Data Overflow</t>
+          <t>Dữ liệu Tràn Bộ Nhớ</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Activating Key</t>
+          <t>Đang kích hoạt chìa khóa</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Barriers</t>
+          <t>Rào Cản</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Sử dụng Cổng để xóa Tham Nhiễm</t>
+          <t>Dùng Cổng để Xóa Nhiễm Độc</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Quick Navigate</t>
+          <t>Định vị nhanh</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Sự kiện mới "Fairy Tale's Finale" đã mở!</t>
+          <t>Sự Kiện Mới "Bản Finale Của Truyện Cổ Tích" Đã Có!</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Quy tắc sự kiện Quà tặng Gió Biển</t>
+          <t>Thể Lệ Sự Kiện Quà Tặng Gió Biển</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Quà tặng của Những giấc mơ thoáng qua</t>
+          <t>Mộng Ảo Phù Du</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Sự kiện [Parade of Stars]</t>
+          <t>["Sự Kiện Diễu Hành Sao Trời"]</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Trang phục</t>
+          <t>Trang Phục</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Pincer Maneuver Warriors I</t>
+          <t>Chiến Binh Mưu Kế Kẹp Nã I</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>HA: Charged I</t>
+          <t>HA: Tấn Công Nạp I</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>HA: Charged II</t>
+          <t>HA: Tích Điện II</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Connecting Portals</t>
+          <t>Đang kết nối Cổng Không Gian</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Connecting Portals</t>
+          <t>Đang kết nối Cổng Không Gian</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Bãi Đầm U Tịch</t>
+          <t>Bãi Đầm Lầy Hẻo Lánh</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Hiểm Họa Thủy Triều</t>
+          <t>Thủy Triều Hiểm Nguy</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Pioneer Project</t>
+          <t>Dự Án Tiên Phong</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Official Community "KURO APP"</t>
+          <t>Ứng Dụng Cộng Đồng Chính Thức "KURO APP"</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Phần thưởng liên kết Email</t>
+          <t>Phần Thưởng Liên Kết Email</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Permanent Event</t>
+          <t>Sự kiện Vĩnh viễn</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Thanh tẩy và Phân tách</t>
+          <t>Thanh Tẩy và Phân Ly</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Đợt Bán Hàng Thần Tốc Ragunna!</t>
+          <t>Đợt Bán Hàng Ragunna!</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Mê Cung Giấc Mộng</t>
+          <t>Mê Cung Somnium</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Mê Cung Giấc Mộng</t>
+          <t>Mê Cung Somnium</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Kẻ Đuổi Theo Vết Nứt</t>
+          <t>Kẻ Đột Kích Hư Không</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Hành Trình Giấc Mộng</t>
+          <t>Hành Trình Mộng Ảo</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Ác mộng quay lại</t>
+          <t>Ác Mộng Quay Trở Lại</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Dream Shard</t>
+          <t>Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Phần thưởng giới hạn thời gian</t>
+          <t>Các Phần Thưởng Giới Hạn</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Rules</t>
+          <t>Luật Lệ</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Khu vực và Tầng</t>
+          <t>Khu và Tầng</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Vigor</t>
+          <t>Sinh Lực</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Area Effect</t>
+          <t>Hiệu ứng khu vực</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Giai đoạn thử nghiệm</t>
+          <t>Giai Đoạn Thử Nghiệm</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Dream Link</t>
+          <t>Liên Kết Giấc Mơ</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Sync Energy I</t>
+          <t>Năng Lượng Đồng Bộ I</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Sync Energy II</t>
+          <t>Năng Lượng Đồng Bộ II</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Illusive Sync</t>
+          <t>Đồng Bộ Ảo Ảnh</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Link Field</t>
+          <t>Vùng Liên Kết</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Illusive Sprint</t>
+          <t>Ảo Ảnh Tốc Độ</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Illusive Sprint: Nhặt lấy Phước Lành</t>
+          <t>Ảo Ảnh Tốc Độ: Thu Thập Phước Lành</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Illusive Sprint: Dash Attack</t>
+          <t>Ảo Ảnh Tốc Độ: Tấn Công Lao Tới</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Hạt giống và Con đường Nở Hoa</t>
+          <t>Những Con Đường Hoa và Hạt</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Hạt giống và Con đường Nở Hoa</t>
+          <t>Những Con Đường Hoa và Hạt</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Dọn sạch Gai Nhọn</t>
+          <t>Gỡ Bỏ Gai Nhọn</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Dọn sạch Gai Nhọn</t>
+          <t>Gỡ Bỏ Gai Nhọn</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Spinning Platforms</t>
+          <t>Nền Đĩa Xoay</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Spinning Platforms</t>
+          <t>Nền Đĩa Xoay</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>About Tactical Simulacra II</t>
+          <t>Về Chiến Dịch Mô Phỏng Chiến Thuật II</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Pincer Maneuver Warriors II</t>
+          <t>Chiến Binh Mưu Kế Kẹp Nã II</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Pincer Maneuver Warriors III</t>
+          <t>Chiến Binh Mưu Kế Kẹp Nã III</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Pincer Maneuver Warriors IV</t>
+          <t>Chiến Binh Mưu Kế Kẹp Nã IV</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Phantom Pain</t>
+          <t>Hologram Chiến Thuật: Nỗi Đau Ảo Ảnh</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless</t>
+          <t>Chop Chop: Không Đầu</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Chest Mimic</t>
+          <t>Rương Biến Hình</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Sentry Construct: Gargoyle</t>
+          <t>Công Trình Tuần Tra: Gargoyle</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Lorelei: Queen of the Night</t>
+          <t>Lorelei: Nữ Hoàng Bóng Đêm</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Chop Chop</t>
+          <t>Nhanh lên nào</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless</t>
+          <t>Chop Chop: Không Đầu</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Chest Mimic</t>
+          <t>Rương Biến Hình</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Sentry Construct: Gargoyle</t>
+          <t>Công Trình Tuần Tra: Gargoyle</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Lorelei: Queen of the Night</t>
+          <t>Lorelei: Nữ Hoàng Bóng Đêm</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless</t>
+          <t>Chop Chop: Không Đầu</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Chop Chop: Leftless/Rightless</t>
+          <t>Chop Chop: Không Tay Trái/Phải</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Kho Lưu Trữ Giai Điệu</t>
+          <t>Lưu Trữ Giai Điệu</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Mask</t>
+          <t>Mặt Nạ</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Beacon of the Past</t>
+          <t>Đèn Hiệu Quá Khứ</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Melody Box</t>
+          <t>Hộp Giai Điệu</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Aria Mummer</t>
+          <t>Diễn Viên Aria</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Cruise Share</t>
+          <t>Chia sẻ Cruise</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Xác nhận lời mời</t>
+          <t>Xác nhận Lời mời</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Kiểm tra ở đâu</t>
+          <t>Kiểm Tra Ở Đâu</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Cách trang bị/gỡ trang bị</t>
+          <t>Cách trang bị/gỡ bỏ</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Ngọn hải đăng quá khứ</t>
+          <t>Đèn Hiệu Quá Khứ</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Echo Challenge: Flight</t>
+          <t>Thử Thách Tiếng Vọng: Bay Lượn</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Fragile Containers</t>
+          <t>Thùng Chứa Mỏng Manh</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Beacon</t>
+          <t>Đèn hiệu</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Sound Emulator</t>
+          <t>Bộ Mô Phỏng Âm Thanh</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Sonance Casket: Ragunna</t>
+          <t>Hòm Thanh Âm: Ragunna</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Làng Thú Nhồi Bông trong Vườn Đã Mất</t>
+          <t>Làng Thú Nhồi Bông Trong Vườn Của Kẻ Lạc Lối</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Gondola: Waterfall Surge</t>
+          <t>Gondola: Sóng Thác Cuộn</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Gondola: Cruising</t>
+          <t>Gondola: Dạo Chơi</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Wingray</t>
+          <t>Tia Cánh</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Công Cụ: Bay Lượn</t>
+          <t>Tiện ích: Bay</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Vitreum Dancer</t>
+          <t>Hologram Chiến Thuật: Vũ Công Vitreum</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Echo Challenge: Plushie Leap</t>
+          <t>Thử Thách Tiếng Vọng: Nhảy Bông Nhồi Bông</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Echo Challenge: Plushie Climber</t>
+          <t>Thử Thách Tiếng Vọng: Leo Núi Thú Nhồi Bông</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Echo Challenge: Plushie Punch</t>
+          <t>Thử Thách Tiếng Vọng: Đấm Bông Nhồi Bông</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Plushie Punch</t>
+          <t>Cú Đấm Bông Gòn</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Nightmare Cloud</t>
+          <t>Đám Mây Ác Mộng</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Echo Challenge: Clear Cloud</t>
+          <t>Thử Thách Tiếng Vọng: Xua Tan Mây Mù</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Echo Challenge: Unfinished Book</t>
+          <t>Thử Thách Tiếng Vọng: Cuốn Sách Chưa Hoàn Thành</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Floating Monument</t>
+          <t>Tượng đài trôi nổi</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Morph Painting Restoration</t>
+          <t>Phục Hồi Bức Họa Hóa Hình</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Dream Patrol: Dreamscape Node</t>
+          <t>Tuần Tra Giấc Mơ: Điểm Nút Cảnh Giới Mộng</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Dream Patrol: Nightmare Node</t>
+          <t>Tuần Tra Giấc Mộng: Nút Ác Mộng</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Dream Patrol: Dreamscape Nexus</t>
+          <t>Tuần Tra Giấc Mơ: Trung Tâm Cảnh Giới Mộng</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Dream Patrol: Fae Ignis from Dreamscape</t>
+          <t>Tuần Tra Giấc Mơ: Fae Ignis from Dreamscape</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Dream Patrol: Plushie Echoes</t>
+          <t>Tuần Tra Giấc Mộng: Plushie Echoes</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Dream Patrol: Broken Glass</t>
+          <t>Tuần Tra Giấc Mơ: Mảnh Kính Vỡ</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Dream Patrol: Blade of Faith</t>
+          <t>Tuần Tra Giấc Mơ: Lưỡi Kiếm Niềm Tin</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Echo Challenge: Clear Cloud</t>
+          <t>Thử Thách Tiếng Vọng: Xua Tan Mây Mù</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Dream Patrol: Roseshroom</t>
+          <t>Tuần Tra Giấc Mộng: Roseshroom</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>The Lifer's Game</t>
+          <t>Trò Chơi Của Kẻ Tù Đày</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>The Lifer's Buffss</t>
+          <t>Hiệu Ứng Của Kẻ Tù Đày</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Fagaceae Formation</t>
+          <t>Hình Thành Fagaceae</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Macabre Torch: Environment Effects</t>
+          <t>Macabre Torch: Hiệu ứng Môi trường</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Stained Glass Restoration</t>
+          <t>Phục Hồi Kính Màu</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Paradimensional Tacet Field</t>
+          <t>Tổ Tacet Siêu Không Gian</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Averardo Vault: Security Protocol</t>
+          <t>Hầm Averardo: Giao Thức Bảo Mật</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Averardo Vault: Vitreum Patroller</t>
+          <t>Hầm Averardo: Tuần Tra Vitreum</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Scatter Prism</t>
+          <t>Lăng Kính Phân Tán</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Alertness</t>
+          <t>Cảnh Giác</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Vault Defense Laser</t>
+          <t>Tia Laser Phòng Thủ Kho Tàng</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Echo Challenge: Wind Trail</t>
+          <t>Thử Thách Tiếng Vọng: Dấu Vết Gió</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Echo Challenge: Wind Ring</t>
+          <t>Thử Thách Tiếng Vọng: Vòng Gió</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Scattered Containers</t>
+          <t>Thùng Hàng Phân Tán</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Floating Containers</t>
+          <t>Thùng chứa trôi nổi</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Overflowing Palette I</t>
+          <t>Bảng Màu Tràn Đầy I</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Overflowing Palette II</t>
+          <t>Bảng Màu Tràn Đầy II</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Overflowing Palette III</t>
+          <t>Bảng Màu Tràn Đầy III</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Sound Emulator</t>
+          <t>Bộ Mô Phỏng Âm Thanh</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Sonance Casket: Ragunna</t>
+          <t>Hòm Thanh Âm: Ragunna</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Làng Thú Nhồi Bông trong Vườn Đã Mất</t>
+          <t>Làng Thú Nhồi Bông Trong Vườn Của Kẻ Lạc Lối</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Gondola: Waterfall Surge</t>
+          <t>Gondola: Sóng Thác Cuộn</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Gondola: Cruising</t>
+          <t>Gondola: Dạo Chơi</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Wingray I</t>
+          <t>Tia Cánh I</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Wingray II</t>
+          <t>Tia Cánh II</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Flight: Availability</t>
+          <t>Bay: Trạng Thái Khả Dụng</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Flight: Steering</t>
+          <t>Bay: Điều Khiển</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Flight: Speeding</t>
+          <t>Bay: Tăng Tốc</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Flight: Stamina Cap</t>
+          <t>Bay: Giới Hạn Thể Lực</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Flight: Cài đặt</t>
+          <t>Bay: Cài Đặt</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Vitreum Dancer</t>
+          <t>Hologram Chiến Thuật: Vũ Công Vitreum</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Leap Spot</t>
+          <t>Điểm Nhảy Cao</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Climbing Spot</t>
+          <t>Điểm Leo Trèo</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Vươn tới đỉnh</t>
+          <t>Nhảy Lên Đỉnh Cao</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Seamrock</t>
+          <t>Đá Nối</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Punch Timing</t>
+          <t>Thời Điểm Đấm</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Powerful Punch</t>
+          <t>Đòn Đấm Uy Lực</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Friable Rock</t>
+          <t>Đá Dễ Vỡ</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Nightmare Cloud: Ordinary</t>
+          <t>Đám Mây Ác Mộng: Thông Thường</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Nightmare Cloud: Sequential</t>
+          <t>Đám Mây Ác Mộng: Liên Tiếp</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Nightmare Cloud: One-off</t>
+          <t>Đám Mây Ác Mộng: Một Lần</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Enhanced Absorption</t>
+          <t>Hấp Thu Được Tăng Cường</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Phát hiện các trang sách bị mất</t>
+          <t>Phát hiện Những Trang Lạc Mất</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Thu thập các trang sách bị mất</t>
+          <t>Đang thu thập Những Trang Giấy Đã Mất</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Kéo bức tượng</t>
+          <t>Kéo Bia Đá</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Khôi phục bức tượng</t>
+          <t>Khôi Phục Đài Kỷ Niệm</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Khôi phục bức tranh Morph</t>
+          <t>Khôi phục Bức Tranh Biến Hình</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Dreamscape Node Tutorial</t>
+          <t>Hướng Dẫn Nút Giấc Mơ</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Nightmare Discord</t>
+          <t>Tacet Discord Ác Mộng</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Defeating Nightmares</t>
+          <t>Tiêu diệt Ác Mộng</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Dreamscape Nexus</t>
+          <t>Trung Tâm Cảnh Mộng</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Tacet Discords Bị Thu Hút Đến Dreamscape Nexus</t>
+          <t>Tacet Discord bị thu hút bởi Nexus Cảnh Mộng</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Fae Ignis Từ Dreamscape</t>
+          <t>Fae Ignis đến từ Giấc Mộng Cảnh</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Plushie Squad Synergy</t>
+          <t>Đồng Đội Bông Gòn</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Plushie Squad Dismissed</t>
+          <t>Đội Bông Gòn Giải Tán</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Broken Glass</t>
+          <t>Mảnh Kính Vỡ</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Blade of Faith</t>
+          <t>Kiếm Đức Tin</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Thường Absorption</t>
+          <t>Hấp thụ Thường</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Roseshroom's Weakness</t>
+          <t>Điểm Yếu của Nấm Hồng</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Moving Pieces</t>
+          <t>Những Mảnh Ghép Di Chuyển</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Black Pieces and Gates</t>
+          <t>Những Mảnh Đen và Cánh Cổng</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Khởi Động Lại Trò Chơi</t>
+          <t>Đang đặt lại trò chơi</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Game Rules</t>
+          <t>Luật Chơi</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Terminal of Blessings</t>
+          <t>Thiết Bị Đầu Cuối Phúc Lành</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Stake of Imbalance</t>
+          <t>Cọc Mất Cân Bằng</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Guarding Altars</t>
+          <t>Canh Giữ Bệ Thờ</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Improving Efficiency</t>
+          <t>Tối Ưu Hóa Hiệu Suất</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Discord Disturbances</t>
+          <t>Nhiễu Loạn Tacet Discord</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Leaving Altar's Range</t>
+          <t>Rời khỏi Phạm vi Bàn thờ</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Dark Area</t>
+          <t>Khu Vực Bóng Tối</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Light Area</t>
+          <t>Khu Vực Ánh Sáng</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Kẻ Thù Dập Tắt Ngọn Đuốc</t>
+          <t>Kẻ địch dập tắt ngọn đuốc</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Nhặt Mảnh Kính Nhuộm Màu</t>
+          <t>Đang nhặt Mảnh Kính Nhuộm Màu</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Placing Stained Glass Pieces</t>
+          <t>Ghép các mảnh kính màu</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Venturing Into Tacet Fields</t>
+          <t>Đột Phá Vào Tổ Tacet</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Vault Surveillance Camera</t>
+          <t>Camera Giám Sát Kho Tàng</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Vitreum Dancers Đang Tuần Tra</t>
+          <t>Đội Vũ Công Vitreum Đang Tuần Tra</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Diệt Mối Đe Dọa Bằng Scatter Prism</t>
+          <t>Loại bỏ Mối Đe Dọa bằng Lăng Kính Phân Tán</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Di Chuyển Một Cách Lén Lút</t>
+          <t>Di Chuyển Tàng Hình</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Defense Laser</t>
+          <t>Tia Laser Phòng Ngự</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Resilience</t>
+          <t>Kiên Cường</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Fragility</t>
+          <t>Sự mong manh</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Sức chịu đựng</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Sức Mạnh</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Động lực</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Inspiration</t>
+          <t>Cảm Hứng</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Shockwave</t>
+          <t>Sóng xung kích</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Hồi phục</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Knockback</t>
+          <t>Hất Văng</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Enhancement: Electro Flare</t>
+          <t>Nâng Cấp: Electro Flare</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Special Elite</t>
+          <t>Đặc Biệt Cao Cấp</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Last Healing</t>
+          <t>Lần Chữa Trị Cuối</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Scorching Aura</t>
+          <t>Hào Quang Nóng Rực</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Insulation</t>
+          <t>Vật liệu cách nhiệt</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Photophobia</t>
+          <t>Ám Sợ Ánh Sáng</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Last Motivation</t>
+          <t>Động Lực Cuối Cùng</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Wrath</t>
+          <t>Thịnh Nộ</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Resilience</t>
+          <t>Kiên Cường</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Fragility</t>
+          <t>Sự mong manh</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t>Sức chịu đựng</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Sức Mạnh</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Motivation</t>
+          <t>Động lực</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Inspiration</t>
+          <t>Cảm Hứng</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Kháng Bất Động</t>
+          <t>Kháng Hóa Bất Động</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Shockwave</t>
+          <t>Sóng xung kích</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Hồi phục</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Knockback</t>
+          <t>Hất Văng</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Enhancement: Aero Erosion</t>
+          <t>Nâng Cấp: Aero Erosion</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Enhancement: Electro Flare</t>
+          <t>Nâng Cấp: Electro Flare</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Tăng Cường: Glacio Chafe</t>
+          <t>Nâng Cấp: Glacio Chafe</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Tăng Cường: Fusion Burst</t>
+          <t>Nâng Cấp: Fusion Burst</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Tăng Cường: Spectro Frazzle</t>
+          <t>Nâng Cấp: Spectro Frazzle</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Tăng Cường: Havoc Bane</t>
+          <t>Nâng Cấp: Havoc Bane</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Special Elite</t>
+          <t>Đặc Biệt Cao Cấp</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Last Healing</t>
+          <t>Lần Chữa Trị Cuối</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Scorching Aura</t>
+          <t>Hào Quang Nóng Rực</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Insulation</t>
+          <t>Vật liệu cách nhiệt</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Photophobia</t>
+          <t>Ám Sợ Ánh Sáng</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Last Motivation</t>
+          <t>Động Lực Cuối Cùng</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Wrath</t>
+          <t>Thịnh Nộ</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Synthesis Mô-đun</t>
+          <t>Mô-đun Tổng hợp</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Immersion Mode</t>
+          <t>Chế độ Hòa Nhập</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Synthesis Mô-đun</t>
+          <t>Mô-đun Tổng hợp</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Immersion Mode</t>
+          <t>Chế độ Hòa Nhập</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Mode Setting</t>
+          <t>Thiết Lập Chế Độ</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Thắp Sáng Ngọn Đuốc Ma Quái</t>
+          <t>Thắp đuốc Tử Thần</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Thắp Sáng Ngọn Đuốc</t>
+          <t>Thắp đuốc</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Dances For Spring's Return</t>
+          <t>Điệu nhảy đón xuân về</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Dream Patrol: Nightmare</t>
+          <t>Tuần Tra Giấc Mộng: Ác Mộng</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Nightmares</t>
+          <t>Ác Mộng</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Báo cáo môi trường</t>
+          <t>Báo cáo Môi trường</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29765,7 +29765,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Sử dụng Dash để tăng tốc Gondola
+          <t>Dùng Dash để tăng tốc Gondola
 Giữ Exit để thoát chế độ lái Gondola</t>
         </is>
       </c>
@@ -29836,7 +29836,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Sử dụng nút tương tác để bơi lên thác nước</t>
+          <t>Nhấn nút tương tác để bơi ngược dòng thác nước</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29906,7 +29906,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Mở Công cụ và truy cập Flight</t>
+          <t>Mở Tiện Ích và truy cập Chức Năng Bay</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29976,7 +29976,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Sử dụng cần điều khiển để bay lên/xuống (lên &amp; xuống) và điều khiển hướng (trái &amp; phải)</t>
+          <t>Dùng cần điều khiển để bay lên/xuống (lên &amp; xuống) và điều chỉnh hướng (trái &amp; phải)</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30046,7 +30046,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Bạn có thể bật chức năng Đảo Ngược Trục Y cho Flight trong Cài Đặt</t>
+          <t>Bạn có thể bật chức năng Đảo Trục Y cho Bay trong Cài Đặt.</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30116,7 +30116,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Bạn có thể bật chức năng Đảo Ngược Trục Y cho Flight trong Cài Đặt</t>
+          <t>Bạn có thể bật chức năng Đảo Trục Y cho Bay trong Cài Đặt.</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30186,7 +30186,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Bạn có thể bật chức năng Đảo Ngược Trục Y cho Flight trong Cài Đặt</t>
+          <t>Bạn có thể bật chức năng Đảo Trục Y cho Bay trong Cài Đặt.</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Đẩy cần điều khiển để di chuyển về phía trước</t>
+          <t>Gạt cần để tiến về phía trước</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30326,7 +30326,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Đẩy cần điều khiển để di chuyển về phía trước</t>
+          <t>Gạt cần để tiến về phía trước</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30396,7 +30396,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Nhấn vào đây để nâng khối nặng lên kích hoạt cơ chế</t>
+          <t>Chạm vào đây để nâng khối nặng lên kích hoạt cơ chế</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30466,7 +30466,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>John Wicktorio: Không Debts for Old Men</t>
+          <t>John Wicktorio: Không Nợ Cũ</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30606,7 +30606,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Glamour Couture</t>
+          <t>Thời Trang Lộng Lẫy</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30676,7 +30676,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Outfits</t>
+          <t>Các Trang Phục</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Chuyện kể trên đảo</t>
+          <t>Huyền Thoại Quần Đảo</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Chiến dịch Lollo: Trở lại</t>
+          <t>Chiến Dịch Lollo: Trở Lại</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30886,7 +30886,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Quà tặng của những giai điệu vui vẻ</t>
+          <t>Mộng Giai Điệu Vui Tươi</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30956,7 +30956,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Di chuyển lén lút</t>
+          <t>Di Chuyển Tàng Hình</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31026,7 +31026,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Carlotta's Secret Weapon</t>
+          <t>Vũ khí bí mật của Carlotta</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31096,7 +31096,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Deep Freeze</t>
+          <t>Đóng Băng Sâu</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Dùng cần điều khiển để điều chỉnh hướng Gondola</t>
+          <t>Dùng cần điều khiển để điều hướng Gondola</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Dùng cần điều khiển để điều chỉnh hướng Gondola</t>
+          <t>Dùng cần điều khiển để điều hướng Gondola</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31376,7 +31376,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Dùng bộ trang sức để bắn và vô hiệu hóa camera giám sát</t>
+          <t>Dùng bộ trang sức bắn hạ và vô hiệu hóa camera giám sát</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31446,7 +31446,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Tactical Hologram: Phantom Pain</t>
+          <t>Hologram Chiến Thuật: Nỗi Đau Ảo Ảnh</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31656,7 +31656,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Wonder Bubbles</t>
+          <t>Những Bong Bóng Kỳ Diệu</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Trawl</t>
+          <t>Kéo lưới</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Cargo</t>
+          <t>Hàng hóa</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31936,7 +31936,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Profile Delivery</t>
+          <t>Giao Hồ sơ</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32006,7 +32006,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Echo Recommendation</t>
+          <t>Gợi Ý Tần Số</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Echo Presets</t>
+          <t>Bản Lưu Tần Số</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32146,7 +32146,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Wuthering Exploration</t>
+          <t>Thám Hiểm Vực Gió</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>About Tactical Simulacra III</t>
+          <t>Về Chiến Dịch Mô Phỏng Chiến Thuật III</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32286,7 +32286,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Nổi giận với bức tượng</t>
+          <t>Thịnh Nộ trước Bức Tượng</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32426,7 +32426,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Nổi giận với bức tượng</t>
+          <t>Thịnh Nộ trước Bức Tượng</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32566,7 +32566,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32636,7 +32636,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Fishing Spots</t>
+          <t>Điểm Câu</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32706,7 +32706,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Mức độ đe dọa vào ban đêm</t>
+          <t>Mức Đe Dọa Ban Đêm</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32776,7 +32776,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Fishing Boat Wheel</t>
+          <t>Bánh Lái Thuyền Câu</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Mutant</t>
+          <t>Đột biến</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32916,7 +32916,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Repairing Pequod</t>
+          <t>Đang sửa Pequod</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32986,7 +32986,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Ảo tưởng Ngàn Cánh Cổng</t>
+          <t>Những Ảo Ảnh Ngàn Cánh Cổng</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33056,7 +33056,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Fishing Spots</t>
+          <t>Điểm Câu</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33126,7 +33126,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Mức độ đe dọa vào ban đêm</t>
+          <t>Mức Đe Dọa Ban Đêm</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33196,7 +33196,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Fishing Boat Wheel</t>
+          <t>Bánh Lái Thuyền Câu</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33266,7 +33266,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Mutant</t>
+          <t>Đột biến</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33336,7 +33336,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Repairing Pequod</t>
+          <t>Đang sửa Pequod</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33406,7 +33406,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Steering Echo Train</t>
+          <t>Điều khiển Tàu Vọng Âm</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Switching Tracks</t>
+          <t>Đang chuyển đổi Nhạc phổ</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33546,7 +33546,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Clearance Devices</t>
+          <t>Thiết Bị Giải Trừ</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33616,7 +33616,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Controlling Echoes</t>
+          <t>Điều khiển Echo</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33686,7 +33686,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Cấp độ Thiết bị Giải trừ</t>
+          <t>Cấp Độ Thiết Bị Giải Trừ</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33756,7 +33756,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Echo Challenge: Dancer Hacking</t>
+          <t>Thử Thách Tiếng Vọng: Vũ Điệu Hacker</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33826,7 +33826,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Tượng Công lý Thần thánh: Trước khi đến</t>
+          <t>Tượng Công Lý Thần Thánh: Trước Khi Đến</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Tượng Công lý Thần thánh: Xuống dưới</t>
+          <t>Tượng Công Lý Thần Thánh: Hạ Giới</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33966,7 +33966,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Boarding Train Echo</t>
+          <t>Đang lên tàu Echo</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34036,7 +34036,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Clearance Command: Echo Train</t>
+          <t>Lệnh Thanh Tra: Echo Train</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34106,7 +34106,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Crossroads</t>
+          <t>Ngã Ba Đường</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34176,7 +34176,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Track Switches</t>
+          <t>Chuyển Đổi Theo Dõi</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34246,7 +34246,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Using Clearance Device</t>
+          <t>Đang sử dụng Thiết Bị Dọn Dẹp</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34316,7 +34316,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Clearance Command: Security Mechanism</t>
+          <t>Lệnh Thanh Tra: Cơ Chế Bảo An</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34386,7 +34386,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Clearance Command: Echo Control</t>
+          <t>Lệnh Thanh Tra: Echo Control</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Clearance Restriction</t>
+          <t>Hạn Chế Giải Trừ</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ Giải trừ</t>
+          <t>Đang nâng cấp Cấp Độ Giải Mã</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34596,7 +34596,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Hiệu ứng Cấp độ Thiết bị Giải trừ</t>
+          <t>Hiệu Ứng Cấp Độ Thiết Bị Giải Trừ</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34666,7 +34666,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Claiming Control</t>
+          <t>Kiểm soát đang được xác nhận</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Controlling Vitreum Dancers</t>
+          <t>Điều khiển Vũ công Pha Lê</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34876,7 +34876,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Đâm bức tượng xuống</t>
+          <t>Đâm Xuống Bức Tượng</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34946,7 +34946,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Về Fantasies of the Thousand Gateways</t>
+          <t>Về Ảo Ảnh Ngàn Cánh Cửa</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Về Fantasies of the Thousand Gateways</t>
+          <t>Về Ảo Ảnh Ngàn Cánh Cửa</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35086,7 +35086,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Về Fantasies of the Thousand Gateways</t>
+          <t>Về Ảo Ảnh Ngàn Cánh Cửa</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35156,7 +35156,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Về Fantasies of the Thousand Gateways</t>
+          <t>Về Ảo Ảnh Ngàn Cánh Cửa</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35226,7 +35226,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Về Fantasies of the Thousand Gateways</t>
+          <t>Về Ảo Ảnh Ngàn Cánh Cửa</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35296,7 +35296,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Về Fantasies of the Thousand Gateways</t>
+          <t>Về Ảo Ảnh Ngàn Cánh Cửa</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35366,7 +35366,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Wuthering Exploration</t>
+          <t>Thám Hiểm Vực Gió</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35436,7 +35436,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Đạt 2.000 Điểm Giai Đoạn</t>
+          <t>Đạt 2.000 Điểm Sân Khấu</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
